--- a/data/Experiment/Raw/Spreadsheets/TheWorks_11242025.xlsx
+++ b/data/Experiment/Raw/Spreadsheets/TheWorks_11242025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernbromley/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA11371-05DF-E244-9F01-64309A24AC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F27509-D908-F64C-918C-AFEF51A4CCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13360" yWindow="760" windowWidth="16040" windowHeight="17200" activeTab="1" xr2:uid="{CA551DF1-0ED1-674A-8F89-05216640288A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="124">
   <si>
     <t>TreeID</t>
   </si>
@@ -406,6 +406,9 @@
   </si>
   <si>
     <t>PIEN60</t>
+  </si>
+  <si>
+    <t>&gt;90%</t>
   </si>
 </sst>
 </file>
@@ -1151,6 +1154,9 @@
       <c r="A32" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="B32">
+        <v>201.7</v>
+      </c>
       <c r="C32" s="4">
         <v>0.1</v>
       </c>
@@ -1159,6 +1165,9 @@
       <c r="A33" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="B33">
+        <v>195.7</v>
+      </c>
       <c r="C33" s="4">
         <v>0.1</v>
       </c>
@@ -1167,6 +1176,9 @@
       <c r="A34" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="B34">
+        <v>203.5</v>
+      </c>
       <c r="C34" s="4">
         <v>0.1</v>
       </c>
@@ -1175,6 +1187,9 @@
       <c r="A35" s="2" t="s">
         <v>36</v>
       </c>
+      <c r="B35">
+        <v>203</v>
+      </c>
       <c r="C35" s="4">
         <v>0.1</v>
       </c>
@@ -1183,6 +1198,9 @@
       <c r="A36" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="B36">
+        <v>197.2</v>
+      </c>
       <c r="C36" s="4">
         <v>0.1</v>
       </c>
@@ -1191,6 +1209,9 @@
       <c r="A37" s="2" t="s">
         <v>38</v>
       </c>
+      <c r="B37">
+        <v>549.6</v>
+      </c>
       <c r="C37" s="4">
         <v>0.1</v>
       </c>
@@ -1199,6 +1220,9 @@
       <c r="A38" s="2" t="s">
         <v>39</v>
       </c>
+      <c r="B38">
+        <v>221.8</v>
+      </c>
       <c r="C38" s="4">
         <v>0.1</v>
       </c>
@@ -1207,6 +1231,9 @@
       <c r="A39" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="B39">
+        <v>199</v>
+      </c>
       <c r="C39" s="4">
         <v>0.1</v>
       </c>
@@ -1215,6 +1242,9 @@
       <c r="A40" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="B40">
+        <v>206.3</v>
+      </c>
       <c r="C40" s="4">
         <v>0.1</v>
       </c>
@@ -1223,6 +1253,9 @@
       <c r="A41" s="2" t="s">
         <v>42</v>
       </c>
+      <c r="B41">
+        <v>245.3</v>
+      </c>
       <c r="C41" s="4">
         <v>0.1</v>
       </c>
@@ -1231,6 +1264,9 @@
       <c r="A42" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="B42">
+        <v>555.6</v>
+      </c>
       <c r="C42" s="4">
         <v>0.1</v>
       </c>
@@ -1239,6 +1275,9 @@
       <c r="A43" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="B43">
+        <v>199.4</v>
+      </c>
       <c r="C43" s="4">
         <v>0.1</v>
       </c>
@@ -1247,14 +1286,20 @@
       <c r="A44" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="B44">
+        <v>195.4</v>
+      </c>
       <c r="C44" s="4">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>46</v>
       </c>
+      <c r="B45">
+        <v>220.3</v>
+      </c>
       <c r="C45" s="4">
         <v>0.1</v>
       </c>
@@ -1263,6 +1308,9 @@
       <c r="A46" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="B46">
+        <v>199.6</v>
+      </c>
       <c r="C46" s="4">
         <v>0.1</v>
       </c>
@@ -1271,6 +1319,9 @@
       <c r="A47" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="B47">
+        <v>552.9</v>
+      </c>
       <c r="C47" s="4">
         <v>0.1</v>
       </c>
@@ -1279,6 +1330,9 @@
       <c r="A48" s="2" t="s">
         <v>49</v>
       </c>
+      <c r="B48">
+        <v>214.9</v>
+      </c>
       <c r="C48" s="4">
         <v>0.1</v>
       </c>
@@ -1287,14 +1341,20 @@
       <c r="A49" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="B49">
+        <v>203</v>
+      </c>
       <c r="C49" s="4">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>51</v>
       </c>
+      <c r="B50">
+        <v>200.7</v>
+      </c>
       <c r="C50" s="4">
         <v>0.1</v>
       </c>
@@ -1303,6 +1363,9 @@
       <c r="A51" s="2" t="s">
         <v>52</v>
       </c>
+      <c r="B51">
+        <v>207.5</v>
+      </c>
       <c r="C51" s="4">
         <v>0.1</v>
       </c>
@@ -1311,6 +1374,9 @@
       <c r="A52" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="B52">
+        <v>195.2</v>
+      </c>
       <c r="C52" s="4">
         <v>0.1</v>
       </c>
@@ -1319,6 +1385,9 @@
       <c r="A53" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="B53">
+        <v>537.70000000000005</v>
+      </c>
       <c r="C53" s="4">
         <v>0.1</v>
       </c>
@@ -1327,6 +1396,9 @@
       <c r="A54" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="B54">
+        <v>226.7</v>
+      </c>
       <c r="C54" s="4">
         <v>0.1</v>
       </c>
@@ -1335,6 +1407,9 @@
       <c r="A55" s="2" t="s">
         <v>56</v>
       </c>
+      <c r="B55">
+        <v>205.6</v>
+      </c>
       <c r="C55" s="4">
         <v>0.1</v>
       </c>
@@ -1343,6 +1418,9 @@
       <c r="A56" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="B56">
+        <v>526.4</v>
+      </c>
       <c r="C56" s="4">
         <v>0.1</v>
       </c>
@@ -1351,6 +1429,9 @@
       <c r="A57" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="B57">
+        <v>211.1</v>
+      </c>
       <c r="C57" s="4">
         <v>0.1</v>
       </c>
@@ -1359,6 +1440,9 @@
       <c r="A58" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="B58">
+        <v>210.3</v>
+      </c>
       <c r="C58" s="4">
         <v>0.1</v>
       </c>
@@ -1367,6 +1451,9 @@
       <c r="A59" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="B59">
+        <v>201.8</v>
+      </c>
       <c r="C59" s="4">
         <v>0.1</v>
       </c>
@@ -1375,6 +1462,9 @@
       <c r="A60" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="B60">
+        <v>201</v>
+      </c>
       <c r="C60" s="4">
         <v>0.1</v>
       </c>
@@ -1383,8 +1473,11 @@
       <c r="A61" s="2" t="s">
         <v>62</v>
       </c>
+      <c r="B61">
+        <v>193.6</v>
+      </c>
       <c r="C61" s="4">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -1745,6 +1838,9 @@
       <c r="A32" s="2" t="s">
         <v>93</v>
       </c>
+      <c r="B32">
+        <v>554.6</v>
+      </c>
       <c r="C32" s="4">
         <v>0.1</v>
       </c>
@@ -1753,6 +1849,9 @@
       <c r="A33" s="2" t="s">
         <v>94</v>
       </c>
+      <c r="B33">
+        <v>206.5</v>
+      </c>
       <c r="C33" s="4">
         <v>0.1</v>
       </c>
@@ -1761,14 +1860,20 @@
       <c r="A34" s="2" t="s">
         <v>95</v>
       </c>
+      <c r="B34">
+        <v>200.9</v>
+      </c>
       <c r="C34" s="4">
-        <v>0.1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>96</v>
       </c>
+      <c r="B35">
+        <v>543.20000000000005</v>
+      </c>
       <c r="C35" s="4">
         <v>0.1</v>
       </c>
@@ -1777,22 +1882,31 @@
       <c r="A36" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C36" s="4">
-        <v>0.1</v>
+      <c r="B36">
+        <v>199.7</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>98</v>
       </c>
+      <c r="B37">
+        <v>189.7</v>
+      </c>
       <c r="C37" s="4">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>99</v>
       </c>
+      <c r="B38">
+        <v>192.6</v>
+      </c>
       <c r="C38" s="4">
         <v>0.1</v>
       </c>
@@ -1801,6 +1915,9 @@
       <c r="A39" s="2" t="s">
         <v>100</v>
       </c>
+      <c r="B39">
+        <v>527.79999999999995</v>
+      </c>
       <c r="C39" s="4">
         <v>0.1</v>
       </c>
@@ -1809,8 +1926,11 @@
       <c r="A40" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="B40">
+        <v>197.5</v>
+      </c>
       <c r="C40" s="4">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -1825,14 +1945,20 @@
       <c r="A42" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C42" s="4">
-        <v>0.1</v>
+      <c r="B42">
+        <v>190.2</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>104</v>
       </c>
+      <c r="B43">
+        <v>504.3</v>
+      </c>
       <c r="C43" s="4">
         <v>0.1</v>
       </c>
@@ -1841,30 +1967,42 @@
       <c r="A44" s="2" t="s">
         <v>105</v>
       </c>
+      <c r="B44">
+        <v>182.8</v>
+      </c>
       <c r="C44" s="4">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C45" s="4">
-        <v>0.1</v>
+      <c r="B45">
+        <v>190.6</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C46" s="4">
-        <v>0.1</v>
+      <c r="B46">
+        <v>201</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>108</v>
       </c>
+      <c r="B47">
+        <v>514.70000000000005</v>
+      </c>
       <c r="C47" s="4">
         <v>0.1</v>
       </c>
@@ -1873,30 +2011,42 @@
       <c r="A48" s="2" t="s">
         <v>109</v>
       </c>
+      <c r="B48">
+        <v>188.9</v>
+      </c>
       <c r="C48" s="4">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>110</v>
       </c>
+      <c r="B49">
+        <v>186.9</v>
+      </c>
       <c r="C49" s="4">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>111</v>
       </c>
+      <c r="B50">
+        <v>190.7</v>
+      </c>
       <c r="C50" s="4">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>112</v>
       </c>
+      <c r="B51">
+        <v>189.6</v>
+      </c>
       <c r="C51" s="4">
         <v>0.1</v>
       </c>
@@ -1905,14 +2055,20 @@
       <c r="A52" s="2" t="s">
         <v>113</v>
       </c>
+      <c r="B52">
+        <v>188.4</v>
+      </c>
       <c r="C52" s="4">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>114</v>
       </c>
+      <c r="B53">
+        <v>197.3</v>
+      </c>
       <c r="C53" s="4">
         <v>0.1</v>
       </c>
@@ -1921,30 +2077,42 @@
       <c r="A54" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C54" s="4">
-        <v>0.1</v>
+      <c r="B54">
+        <v>192.1</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>116</v>
       </c>
+      <c r="B55">
+        <v>186</v>
+      </c>
       <c r="C55" s="4">
-        <v>0.1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>117</v>
       </c>
+      <c r="B56">
+        <v>183.2</v>
+      </c>
       <c r="C56" s="4">
-        <v>0.1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>118</v>
       </c>
+      <c r="B57">
+        <v>199.3</v>
+      </c>
       <c r="C57" s="4">
         <v>0.1</v>
       </c>
@@ -1953,14 +2121,20 @@
       <c r="A58" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C58" s="4">
-        <v>0.1</v>
+      <c r="B58">
+        <v>190.4</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>120</v>
       </c>
+      <c r="B59">
+        <v>196.5</v>
+      </c>
       <c r="C59" s="4">
         <v>0.1</v>
       </c>
@@ -1969,6 +2143,9 @@
       <c r="A60" s="2" t="s">
         <v>121</v>
       </c>
+      <c r="B60">
+        <v>188.3</v>
+      </c>
       <c r="C60" s="4">
         <v>0.1</v>
       </c>
@@ -1976,6 +2153,9 @@
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>122</v>
+      </c>
+      <c r="B61">
+        <v>189.4</v>
       </c>
       <c r="C61" s="4">
         <v>0.1</v>
